--- a/output/HS_Code_Summary_Everest_Ayurveda_32627.xlsx
+++ b/output/HS_Code_Summary_Everest_Ayurveda_32627.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="HS Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Dokumenty a poznámky" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Kontroly a clo (TARIC)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HS Summary'!$A$7:$L$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HS Summary'!$A$7:$Q$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +53,12 @@
       <color rgb="001F3864"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +78,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -130,6 +140,10 @@
     <xf numFmtId="4" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -495,21 +509,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -588,15 +607,40 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
+          <t>Fytokontrola / TRACES</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>Vet. kontrola (SVD)</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>Povinné kódy do JSD</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>Clo MFN</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>Clo GSP (preference)</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
           <t>CBAM</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>Antidumping</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>Poznámka</t>
         </is>
@@ -640,17 +684,42 @@
       <c r="I8" s="9" t="n">
         <v>2483.2</v>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Y929</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>0 %</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>0 % (bez GSP)</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
         <is>
           <t>Ne – nespadá pod CBAM</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>Potravina – vstupní kontrola / CHED dle potřeby.</t>
         </is>
@@ -694,17 +763,42 @@
       <c r="I9" s="9" t="n">
         <v>6997.2</v>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Y929</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>8,30 %</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>4,80 %</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
         <is>
           <t>Ne – nespadá pod CBAM</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr"/>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -744,17 +838,42 @@
       <c r="I10" s="9" t="n">
         <v>17355</v>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Y929</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>24,00 % + 4,20 EUR/100 kg</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>20,40 % + 4,20 EUR/100 kg</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
         <is>
           <t>Ne – nespadá pod CBAM</t>
         </is>
       </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr"/>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -794,17 +913,42 @@
       <c r="I11" s="9" t="n">
         <v>5780</v>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Y929</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>24,00 % + 23,00 EUR/100 kg</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>20,50 % + 23,00 EUR/100 kg</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
         <is>
           <t>Ne – nespadá pod CBAM</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr"/>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -844,17 +988,42 @@
       <c r="I12" s="9" t="n">
         <v>1500</v>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Y929</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>20,80 %</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>17,30 %</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
         <is>
           <t>Ne – nespadá pod CBAM</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr"/>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -894,17 +1063,42 @@
       <c r="I13" s="9" t="n">
         <v>1372.8</v>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>Y929</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>19,20 %</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>13,40 %</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
         <is>
           <t>Ne – nespadá pod CBAM</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr"/>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -944,17 +1138,42 @@
       <c r="I14" s="9" t="n">
         <v>2496</v>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Y929</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>19,20 %</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>13,40 %</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
         <is>
           <t>Ne – nespadá pod CBAM</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr"/>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="Q14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -994,17 +1213,42 @@
       <c r="I15" s="9" t="n">
         <v>7725</v>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>ANO – podmíněné</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Y929 + Y930</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>13,00 %</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>9,50 %</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
         <is>
           <t>Ne – nespadá pod CBAM</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr"/>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1044,17 +1288,42 @@
       <c r="I16" s="9" t="n">
         <v>13325</v>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>ANO – podmíněné</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Y929 + Y930</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>20,80 %</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>17,30 %</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
         <is>
           <t>Ne – nespadá pod CBAM</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr"/>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1094,17 +1363,42 @@
       <c r="I17" s="9" t="n">
         <v>1638.4</v>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>Y900 + Y113 + Y160</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>0 %</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>0 % (bez GSP)</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
         <is>
           <t>Ne – nespadá pod CBAM</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
         <is>
           <t>Kosmetický přípravek – ověřit oznámení do CPNP (nařízení 1223/2009).</t>
         </is>
@@ -1148,17 +1442,42 @@
       <c r="I18" s="9" t="n">
         <v>1126.4</v>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>Y113 + Y160</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>0 %</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>0 % (bez GSP)</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
         <is>
           <t>Ne – nespadá pod CBAM</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
         <is>
           <t>Kosmetický přípravek – ověřit oznámení do CPNP (nařízení 1223/2009).</t>
         </is>
@@ -1202,17 +1521,42 @@
       <c r="I19" s="9" t="n">
         <v>2150.4</v>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Y900 + Y113 + Y160 + Y924</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>6,50 %</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>0 %</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
         <is>
           <t>Ne – nespadá pod CBAM</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>Kosmetický přípravek – ověřit oznámení do CPNP (nařízení 1223/2009).</t>
         </is>
@@ -1256,17 +1600,42 @@
       <c r="I20" s="9" t="n">
         <v>1185.75</v>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>0 %</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>0 % (bez GSP)</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
         <is>
           <t>Ne – nespadá pod CBAM</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr"/>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="Q20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -1293,6 +1662,11 @@
       <c r="J21" s="10" t="n"/>
       <c r="K21" s="10" t="n"/>
       <c r="L21" s="10" t="n"/>
+      <c r="M21" s="10" t="n"/>
+      <c r="N21" s="10" t="n"/>
+      <c r="O21" s="10" t="n"/>
+      <c r="P21" s="10" t="n"/>
+      <c r="Q21" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1309,7 +1683,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:L20"/>
+  <autoFilter ref="A7:Q20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1776,4 +2150,965 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Ověření v TARIC – dovoz z Indie (IN), referenční datum 14-09-2026, poslední aktualizace TARIC 11-09-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Zdroj: ec.europa.eu/taxation_customs/dds2/taric – opatření a podmínky načteny pro každý CN kód zvlášť (oblast IN). Odpověď na dotaz Maurice Ward ze dne 14.09.2026 (fytokontrola / TRACES / SVD).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>CN kód</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Zboží</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Fytokontrola / TRACES-PP</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Veterinární kontrola (SVD / CHED-P)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Povinné kódy do JSD</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Clo MFN (třetí země)</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Clo GSP (preference)</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Clo bez preference EUR</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Clo s preferencí EUR</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Úspora EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>0902300000</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Černý čaj sáčkový (Masala Chai)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Y929</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>0 %</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>0 % (bez GSP)</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>1106309080</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Amla v prášku, bez přidaných látek</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Y929</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>8,30 %</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>4,80 %</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>580.77</v>
+      </c>
+      <c r="I6" s="9" t="n">
+        <v>335.87</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>244.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>2007101095</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Bylinné džemy – řada PRASH (Rasa, Rakta, Mamsa, Meda, Asthi, Majja, Shukra, Arthava, Anna, Prana, Ambu, Purisha, Mutra, Sveda, Mano, Nayana, Kesha)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Y929</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>24,00 % + 4,20 EUR/100 kg</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>20,40 % + 4,20 EUR/100 kg</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>4269.78</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>3645</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>624.78</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>2007993980</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Bylinný džem CHYAWANPRASH</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Y929</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>24,00 % + 23,00 EUR/100 kg</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>20,50 % + 23,00 EUR/100 kg</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>1621.8</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>1419.5</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>202.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>2008207100</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Sušený ananas</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Y929</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>20,80 %</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>17,30 %</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>312</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>259.5</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>2008977819</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Amla nutriční tyčinka VATA</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Y929</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>19,20 %</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>13,40 %</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>263.58</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>183.96</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>79.62</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>2008977890</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Amla nutriční tyčinka (Pitta, Kapha)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Y929</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>19,20 %</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>13,40 %</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>479.23</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>334.46</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>144.77</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>2008996390</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Sušené ovoce – jackfruit, mango, papája, guava</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>ANO – podmíněné</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>Y929 + Y930</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>13,00 %</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>9,50 %</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>1004.25</v>
+      </c>
+      <c r="I12" s="9" t="n">
+        <v>733.88</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>270.38</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>2008996799</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Sušená amla (Amla candy)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>ANO – podmíněné</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>Y929 + Y930</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>20,80 %</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>17,30 %</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>2771.6</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>2305.22</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>466.38</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>3304990000</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Kosmetický přípravek pro péči o pokožku – VATA body care olej</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Y900 + Y113 + Y160</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>0 %</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>0 % (bez GSP)</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>3305900000</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Vlasový olej – BHRINGARAJ hair care oil</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Y113 + Y160</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>0 %</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>0 % (bez GSP)</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>3307900000</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Masážní olej MAHANARAYAN</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Y900 + Y113 + Y160 + Y924</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>6,50 %</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>0 %</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>139.78</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>139.78</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>4819200000</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Papírové skládací krabičky (potištěné)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>0 %</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>0 % (bez GSP)</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>CELKEM</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="12" t="n">
+        <v>11442.78</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>9217.379999999999</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>2225.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>ZÁVĚR K DOTAZU MAURICE WARD (14.09.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>1) Fytosanitární kontrola / TRACES-PP: NE – ani jeden z 13 CN kódů nemá v TARIC fytosanitární opatření.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Není třeba rostlinolékařské osvědčení (N851) ani CHED-PP, není třeba registrace v TRACES.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Důvod: veškeré rostlinné zboží je zpracované (sušené, kandované, džemy, prášek, fermentovaný čaj),</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   tj. mimo přílohu XI nařízení (EU) 2019/2072.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   JEDINÁ výjimka se netýká zboží, ale OBALU: zásilka obsahuje 11 palet – pokud jsou dřevěné, musí být</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ošetřené a označené dle ISPM 15. To je jediný fytosanitární požadavek této zásilky.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>2) Veterinární doklad SVD / CHED-P: NE – žádná položka není produktem živočišného původu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ALE POZOR: u CN 2008 99 63 90 a 2008 99 67 99 je v TARIC PODMÍNĚNÉ veterinární opatření</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (nařízení (EU) 2021/632, platné od 23-07-2026). Celní prohlášení proto MUSÍ u těchto dvou položek</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   nést jeden z kódů:</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      • Y930 – „zboží není dotčeno nařízením (EU) 2021/632“  ← TOTO PLATÍ PRO NAŠI ZÁSILKU</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      • N853 – CHED-P (jen pokud by šlo o složený produkt se živočišnou složkou)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      • Y931 – výjimka dle čl. 3 nař. (EU) 2021/630 (trvanlivé složené produkty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Bez Y930 (nebo N853) JSD u těchto dvou položek neprojde. SVD se ale nevystavuje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3) Bio kontrola: všech 9 potravinových kódů má opatření „Import control of organic products“</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (nař. 2021/2306). Zboží není bio → uvést Y929 „zboží není dotčeno nařízením (EU) 2018/848“.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Pokud by šlo o bio, bylo by třeba C644 (certifikát o kontrole).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>4) Kosmetika (3304 99 00 00, 3305 90 00 00, 3307 90 00 00) – opatření CITES, REACH, F-plyny, rtuť.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Zboží se jich netýká → Y900 (není CITES), Y113 (mimo přílohu XVII REACH), Y160 (mimo nař. 2024/573),</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   u 3307 90 navíc Y924 (mimo nař. 2017/852 o rtuti). U 3305 90 se CITES opatření nevyskytuje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>5) Zvýšené kontroly potravin nerostlinného původu (nař. 2019/1793): žádný z kódů není v TARIC dotčen,</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   tedy ani CHED-D. Antidumping: žádný.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>K OVĚŘENÍ S VÝVOZCEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>Chyawanprash a řada „prash“ tradičně obsahují ghí (mléčný tuk) a med – tedy složky živočišného původu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>V TARIC nemá CN 2007 10 10 95 ani 2007 99 39 80 žádné veterinární opatření, takže k celnímu prohlášení</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>není u nich nic potřeba. Přesto doporučuji si od vývozce vyžádat složení: pokud by živočišná složka byla</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>i v položkách pod 2008 99 (amla candy, sušené ovoce), nebyl by Y930 správný a musel by se použít Y931</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>nebo N853. Dle popisu jde o ovoce v cukru bez živočišných složek → Y930.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>DOPAD PREFERENCE (GSP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Výpočet výše je z fakturované hodnoty FOB. Skutečná celní hodnota bude vyšší o dopravu a pojištění</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>do místa vstupu do EU (freight collect), takže i clo bude odpovídajícím způsobem vyšší.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>Preferenční věta (REX INREX3113021227EC010) tedy na této zásilce šetří přibližně 2 225 EUR.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>